--- a/椙山改修/増減_見積内訳_索引.xlsx
+++ b/椙山改修/増減_見積内訳_索引.xlsx
@@ -31,16 +31,438 @@
     <t xml:space="preserve">出典：椙山改修/参考/260904_見積内訳書（契約・原価）.pdf（2026/9/4 出力、101頁。左＝見積、右＝原価）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">基準金額（契約金額）：契約書待ち。</t>
-    </r>
+    <t xml:space="preserve">基準金額（契約金額）：契約書待ち。5/28 見積（No.260007）と 9/4 見積内訳書のどちらが契約の基準かは契約書で確定する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">階層</t>
+  </si>
+  <si>
+    <t xml:space="preserve">番号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">名称</t>
+  </si>
+  <si>
+    <t xml:space="preserve">頁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">見積金額</t>
+  </si>
+  <si>
+    <t xml:space="preserve">原価金額</t>
+  </si>
+  <si>
+    <t xml:space="preserve">照合（下位の合計との差）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">共通仮設工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">解体撤去工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b)-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　建築工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　撤去工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p6-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b)-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p9-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　幹線設備工事（電気）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　照明器具設備工事（電気）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　電灯設備工事（電気）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　誘導灯設備工事（電気）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　コンセント設備工事（電気）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p15-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　LAN設備工事（電気）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p17-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　放送設備工事（電気）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p19-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　自動火災報知設備工事（電気）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p21-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　ダクト撤去工事（空調）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p23-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　配管撤去工事（衛生）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p25-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">改修工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c)-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　直接仮設工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p29-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　躯体工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　防水工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　タイル工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　金属工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p35-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　金属製建具工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　ガラス工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　木工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p41-43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　左官工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　塗装工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p45-46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　内装工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p47-48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　雑工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p49-52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　　サイン工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　　その他雑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p51-52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c)-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　電気設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　幹線設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p54-55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　空調電源設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p56-58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　照明器具設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p59-61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　電灯設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p62-66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　誘導灯設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p67-69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　コンセント設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p70-73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　LAN設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p74-75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　放送設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p76-78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　自動火災報知設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p79-81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c)-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　空気調和設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　空調機器設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p83-84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　配管設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　　冷媒配管設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p86-87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　　ドレン配管設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p88-89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　空調ダクト設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p90-92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c)-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　衛生設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　給水設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p94-95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　給湯設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p96-97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　屋内排水通気設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p98-99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　衛生器具設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p100-101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">諸経費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　設備管理費（原価のみ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　内勤工事経費（原価のみ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">工事価格（a〜d の合計）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">内訳書 p1「計」：見積 262,000,000／原価 222,477,594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">内訳書の記載との差</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -50,7 +472,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">5/28 </t>
+      <t xml:space="preserve">0 </t>
     </r>
     <r>
       <rPr>
@@ -60,520 +482,97 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">見積（</t>
-    </r>
+      <t xml:space="preserve">なら一致</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">消費税及び地方消費税</t>
+  </si>
+  <si>
+    <t xml:space="preserve">内訳書 p1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">合計（税込）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">288,200,000</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="9"/>
+        <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">No.260007</t>
+      <t xml:space="preserve">5/28 </t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="9"/>
+        <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）と </t>
+      <t xml:space="preserve">見積（</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="9"/>
+        <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">9/4 </t>
+      <t xml:space="preserve">No.260007</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="9"/>
+        <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">見積内訳書のどちらが契約の基準かは契約書で確定する</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">階層</t>
-  </si>
-  <si>
-    <t xml:space="preserve">番号</t>
-  </si>
-  <si>
-    <t xml:space="preserve">名称</t>
-  </si>
-  <si>
-    <t xml:space="preserve">頁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">見積金額</t>
-  </si>
-  <si>
-    <t xml:space="preserve">原価金額</t>
-  </si>
-  <si>
-    <t xml:space="preserve">照合（下位の合計との差）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">共通仮設工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">解体撤去工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b)-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　建築工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　撤去工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p6-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b)-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p9-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　幹線設備工事（電気）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　照明器具設備工事（電気）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　電灯設備工事（電気）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　誘導灯設備工事（電気）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　コンセント設備工事（電気）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p15-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　LAN設備工事（電気）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p17-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　放送設備工事（電気）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p19-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　自動火災報知設備工事（電気）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p21-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　ダクト撤去工事（空調）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p23-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　配管撤去工事（衛生）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p25-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">改修工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c)-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　直接仮設工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p29-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　躯体工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　防水工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　タイル工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　金属工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p35-38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　金属製建具工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　ガラス工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　木工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p41-43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　左官工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　塗装工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p45-46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　内装工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p47-48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　雑工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p49-52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　　サイン工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　　その他雑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p51-52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c)-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　電気設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　幹線設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p54-55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　空調電源設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p56-58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　照明器具設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p59-61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　電灯設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p62-66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　誘導灯設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p67-69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　コンセント設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p70-73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　LAN設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p74-75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　放送設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p76-78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　自動火災報知設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p79-81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c)-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　空気調和設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　空調機器設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p83-84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　配管設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　　冷媒配管設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p86-87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　　ドレン配管設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p88-89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　空調ダクト設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p90-92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c)-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　衛生設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　給水設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p94-95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　給湯設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p96-97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　屋内排水通気設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p98-99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　衛生器具設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p100-101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">諸経費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　設備管理費（原価のみ）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　内勤工事経費（原価のみ）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">工事価格（a〜d の合計）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">内訳書 p1「計」：見積 262,000,000／原価 222,477,594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">内訳書の記載との差</t>
-  </si>
-  <si>
+      <t xml:space="preserve">）食堂分 と </t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="9"/>
+        <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0 </t>
+      <t xml:space="preserve">9/4 </t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="9"/>
+        <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">なら一致</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">消費税及び地方消費税</t>
-  </si>
-  <si>
-    <t xml:space="preserve">内訳書 p1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">合計（税込）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">288,200,000</t>
+      <t xml:space="preserve">見積内訳書 の比較（税抜・見積金額）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">基準金額：契約書待ち。理由欄は【事実】＝両方の明細で確認、【推測】＝明細の照合はしていない／理由は書類に書かれていない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">工種</t>
   </si>
   <si>
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="12"/>
+        <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
         <family val="0"/>
@@ -584,38 +583,45 @@
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="12"/>
+        <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">見積（</t>
-    </r>
+      <t xml:space="preserve">見積</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="12"/>
+        <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">No.260007</t>
+      <t xml:space="preserve">9/4 </t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="12"/>
+        <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）食堂分 と </t>
-    </r>
+      <t xml:space="preserve">内訳書</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">差額（9/4−5/28）</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="12"/>
+        <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
         <family val="0"/>
@@ -626,141 +632,170 @@
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="12"/>
+        <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">見積内訳書 の比較（税抜・見積金額）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">基準金額：契約書待ち。理由欄は【事実】＝両方の明細で確認、【推測】＝明細の照合はしていない／理由は書類に書かれていない</t>
-  </si>
-  <si>
-    <t xml:space="preserve">工種</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">頁</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">下がった理由</t>
+  </si>
+  <si>
+    <t xml:space="preserve">変更なし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">解体撤去／建築（撤去工事）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【事実】床テラゾー撤去 358m2→189m2、天井材撤去 366m2（下地共）→64m2（下地共）＋302m2（下地残置）、産廃の量を減（コンガラ 20→12m3、がれき 8→5m3）、諸雑費 499,000→351,090、有価物買取 ▲80,000→▲40,000。【推測】撤去範囲の見直し</t>
+  </si>
+  <si>
+    <t xml:space="preserve">解体撤去／設備</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p9-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c)-1-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">直接仮設工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【事実】食堂外部東の足場 190.7m2→45.53m2 など。【推測】足場範囲の見直し</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">5/28 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">c)-1-2</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">見積</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">9/4 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">内訳書</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">差額（</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">4</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">躯体・防水・タイル工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p32-34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c)-1-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金属工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【推測】明細は未照合</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">9/4−5/28</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">c)-1-6</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">9/4 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">頁</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">下がった理由</t>
-  </si>
-  <si>
-    <t xml:space="preserve">変更なし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">解体撤去／建築（撤去工事）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">【事実】床テラゾー撤去 </t>
-    </r>
+      <t xml:space="preserve">8</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">金属製建具・ガラス・木工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p39-43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c)-1-9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">左官工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【事実】5/28 は床・壁 MORTEX（634m2：プライマー・クラック防水処理・3回塗り・トップコート、計 約4,390万円）を左官で計上。9/4 では左官から外れ、床タイル下地などだけが残る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c)-1-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">塗装工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【事実】9/4 はジョリパッド モルタルアート（壁 339m2・床 290m2・天井 5m2）を塗装で計上（約2,450万円）。左官＋塗装の合計は 47,635,312→28,135,312（▲19,500,000）。【推測】仕上材の変更（VE）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c)-1-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">内装工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c)-1-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雑工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c)-2-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">電気／照明器具設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【推測】器具の見直し（明細は未照合）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c)-2-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">電気／電灯設備工事</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -769,7 +804,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">358m2→189m2</t>
+      <t xml:space="preserve">c)-2 </t>
     </r>
     <r>
       <rPr>
@@ -778,122 +813,237 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">、天井材撤去 </t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">他</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">電気／その他（幹線・空調電源・誘導灯・コンセント・LAN・放送・自火報）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p53-81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">空気調和設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p82-92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">衛生設備工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p93-101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【推測】工事費の減額に合わせた調整</t>
+  </si>
+  <si>
+    <t xml:space="preserve">工事価格（税抜）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">366m2</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">5/28 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（下地共）→</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">食堂分：税抜 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">64m2</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">305,000,000</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（下地共）＋</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">（税込 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">302m2</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">335,500,000</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（下地残置）、産廃の量を減（コンガラ </t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">）。</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20→12m3</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">9/4</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">、がれき </t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8→5m3</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">262,000,000</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）、諸雑費 </t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">（税込 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">499,000→351,090</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">288,200,000</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">、有価物買取 ▲</t>
-    </r>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">消費税</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参考：5/28 見積 No.260007 の全体（税込）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 大学会館食堂リニューアル工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">② 外構リニューアル工事 さくら坂整備</t>
+  </si>
+  <si>
+    <t xml:space="preserve">③ 外構リニューアル工事 キャンパスコモン整備</t>
+  </si>
+  <si>
+    <t xml:space="preserve">④ 外構リニューアル工事 10000歩コース整備</t>
+  </si>
+  <si>
+    <t xml:space="preserve">計（税込）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">うち工事価格（税抜）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">増減 No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">項目</t>
+  </si>
+  <si>
+    <t xml:space="preserve">内訳書の該当</t>
+  </si>
+  <si>
+    <t xml:space="preserve">見積金額（内訳書）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">契約に含まれるか</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メモ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アスベスト含有建材事前調査</t>
+  </si>
+  <si>
+    <t xml:space="preserve">撤去工事「石綿含有 石膏ボード運搬・処分費（管理型）7m3」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">含まれる（処分費のみ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">石綿の除去作業の項目は無し → 580,000 は除去・処分等の追加分として別途（増額）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">撤去工事「石綿含有 がれき運搬・処分費（安定型）11m3」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">共通仮設「試験調査」1式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">含まれる（小山さん確認）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アスベストの事前調査の費用はここに含まれる（10/31 小山さん確認）</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -902,7 +1052,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">80,000→▲40,000</t>
+      <t xml:space="preserve">2</t>
     </r>
     <r>
       <rPr>
@@ -911,20 +1061,14 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">。【推測】撤去範囲の見直し</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">解体撤去／設備</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p9-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c)-1-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">直接仮設工事</t>
+      <t xml:space="preserve">階プランター撤去</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">撤去工事「プランターBOX撤去」7か所（吹き抜け側）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">含まれる</t>
   </si>
   <si>
     <r>
@@ -934,7 +1078,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">【事実】食堂外部東の足場 </t>
+      <t xml:space="preserve">吹き抜け側は契約内。</t>
     </r>
     <r>
       <rPr>
@@ -944,7 +1088,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">190.7m2→45.53m2 </t>
+      <t xml:space="preserve">2</t>
     </r>
     <r>
       <rPr>
@@ -953,10 +1097,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">など。【推測】足場範囲の見直し</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">階プランターの内側（室内側）の撤去は契約外 → 追加見積 </t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
@@ -965,7 +1107,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">c)-1-2</t>
+      <t xml:space="preserve">650,000 </t>
     </r>
     <r>
       <rPr>
@@ -974,7 +1116,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">〜</t>
+      <t xml:space="preserve">を提出、不採用（撤去しない）（</t>
     </r>
     <r>
       <rPr>
@@ -984,34 +1126,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">躯体・防水・タイル工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p32-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c)-1-5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金属工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">【推測】明細は未照合</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">c)-1-6</t>
+      <t xml:space="preserve">10/31 </t>
     </r>
     <r>
       <rPr>
@@ -1020,770 +1135,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">金属製建具・ガラス・木工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p39-43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c)-1-9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">左官工事</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">【事実】</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5/28 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">は床・壁 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MORTEX</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">634m2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：プライマー・クラック防水処理・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回塗り・トップコート、計 約</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4,390</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万円）を左官で計上。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">では左官から外れ、床タイル下地などだけが残る</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">c)-1-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">塗装工事</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">【事実】</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">はジョリパッド モルタルアート（壁 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">339m2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・床 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">290m2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・天井 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5m2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）を塗装で計上（約</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2,450</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万円）。左官＋塗装の合計は </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">47,635,312→28,135,312</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（▲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">19,500,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）。【推測】仕上材の変更（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">VE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">c)-1-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">内装工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c)-1-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雑工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c)-2-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">電気／照明器具設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">【推測】器具の見直し（明細は未照合）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c)-2-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">電気／電灯設備工事</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">c)-2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">他</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">電気／その他（幹線・空調電源・誘導灯・コンセント・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">LAN</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・放送・自火報）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p53-81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">空気調和設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p82-92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">衛生設備工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p93-101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">【推測】工事費の減額に合わせた調整</t>
-  </si>
-  <si>
-    <t xml:space="preserve">工事価格（税抜）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5/28 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">食堂分：税抜 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">305,000,000</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（税込 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">335,500,000</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）。</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/4</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">262,000,000</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（税込 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">288,200,000</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">消費税</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">参考：</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5/28 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">見積 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">No.260007 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の全体（税込）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">① 大学会館食堂リニューアル工事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">② 外構リニューアル工事 さくら坂整備</t>
-  </si>
-  <si>
-    <t xml:space="preserve">③ 外構リニューアル工事 キャンパスコモン整備</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">④ 外構リニューアル工事 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">歩コース整備</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">計（税込）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">うち工事価格（税抜）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">増減 No.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">項目</t>
-  </si>
-  <si>
-    <t xml:space="preserve">内訳書の該当</t>
-  </si>
-  <si>
-    <t xml:space="preserve">見積金額（内訳書）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">契約に含まれるか</t>
-  </si>
-  <si>
-    <t xml:space="preserve">メモ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アスベスト含有建材事前調査</t>
-  </si>
-  <si>
-    <t xml:space="preserve">撤去工事「石綿含有 石膏ボード運搬・処分費（管理型）7m3」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">含まれる（処分費のみ）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">石綿の除去作業・含有分析の項目は無し → 580,000 は別途（増額）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同上</t>
-  </si>
-  <si>
-    <t xml:space="preserve">撤去工事「石綿含有 がれき運搬・処分費（安定型）11m3」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">共通仮設「試験調査」1式</t>
-  </si>
-  <si>
-    <t xml:space="preserve">内容の記載なし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">事前調査が含まれるかは不明（要確認）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">階プランター撤去</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">撤去工事「プランターBOX撤去」7か所</t>
-  </si>
-  <si>
-    <t xml:space="preserve">含まれる</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">階プランター（外部・室内側）と同じものかは要確認。増減 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">No.2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">は不採用</t>
+      <t xml:space="preserve">小山さん確認）</t>
     </r>
   </si>
   <si>
@@ -1799,61 +1151,10 @@
     <t xml:space="preserve">金属製建具工事「オペレーター改修 取付運搬費」1か所</t>
   </si>
   <si>
-    <t xml:space="preserve">計 430,600。480,000／520,000 との関係（差額か追加か）は要確認</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">別途工事・支給品（</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5/28 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">見積 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">No.260007</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">「別途工事」シートの転記）</t>
-    </r>
+    <t xml:space="preserve">計 430,600。10/31 現地調査で2パターン必要と分かり 480,000／520,000 の2案を別途の追加見積として提出（小山さん確認）。契約分との関係は2案の内容で要確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">別途工事・支給品（5/28 見積 No.260007「別途工事」シートの転記）</t>
   </si>
   <si>
     <t xml:space="preserve">見積に含まれないもの。これに当たる工事を頼まれたら増減リストに「増額（別途工事）」として載せる候補</t>
@@ -1871,34 +1172,7 @@
     <t xml:space="preserve">既設解体</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">食堂改修の撤去工事（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">b</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）は本工事。ここでいう既設解体の範囲は要確認</t>
-    </r>
+    <t xml:space="preserve">食堂改修の撤去工事（b）は本工事。ここでいう既設解体の範囲は要確認</t>
   </si>
   <si>
     <t xml:space="preserve">地中障害物除去</t>
@@ -2179,9 +1453,17 @@
       <color rgb="FFFF0000"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="HG丸ｺﾞｼｯｸM-PRO"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="HG丸ｺﾞｼｯｸM-PRO"/>
@@ -2194,14 +1476,6 @@
       <color rgb="FFFF0000"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="HG丸ｺﾞｼｯｸM-PRO"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -2286,7 +1560,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2303,11 +1577,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2315,7 +1589,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2323,15 +1597,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2339,11 +1613,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2351,7 +1625,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2359,71 +1633,51 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2700,7 +1954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -3993,564 +3247,564 @@
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="70"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="19" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
+    <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="5" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="24" t="n">
+      <c r="C5" s="22" t="n">
         <v>4540000</v>
       </c>
-      <c r="D5" s="24" t="n">
+      <c r="D5" s="22" t="n">
         <v>4540000</v>
       </c>
-      <c r="E5" s="24" t="n">
+      <c r="E5" s="22" t="n">
         <f aca="false">D5-C5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" s="21" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="22" t="n">
         <v>7960000</v>
       </c>
-      <c r="D6" s="24" t="n">
+      <c r="D6" s="22" t="n">
         <v>5700000</v>
       </c>
-      <c r="E6" s="24" t="n">
+      <c r="E6" s="22" t="n">
         <f aca="false">D6-C6</f>
         <v>-2260000</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="21" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="22" t="n">
         <v>10990000</v>
       </c>
-      <c r="D7" s="24" t="n">
+      <c r="D7" s="22" t="n">
         <v>10990000</v>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="22" t="n">
         <f aca="false">D7-C7</f>
         <v>0</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="F7" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G7" s="21" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="22" t="n">
         <v>4826702</v>
       </c>
-      <c r="D8" s="24" t="n">
+      <c r="D8" s="22" t="n">
         <v>4345372</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="22" t="n">
         <f aca="false">D8-C8</f>
         <v>-481330</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="23" t="s">
+      <c r="G8" s="21" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C9" s="22" t="n">
         <v>15801300</v>
       </c>
-      <c r="D9" s="24" t="n">
+      <c r="D9" s="22" t="n">
         <v>15801300</v>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="22" t="n">
         <f aca="false">D9-C9</f>
         <v>0</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G9" s="23" t="s">
+      <c r="G9" s="21" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="C10" s="24" t="n">
+      <c r="C10" s="22" t="n">
         <v>20138838</v>
       </c>
-      <c r="D10" s="24" t="n">
+      <c r="D10" s="22" t="n">
         <v>18986738</v>
       </c>
-      <c r="E10" s="24" t="n">
+      <c r="E10" s="22" t="n">
         <f aca="false">D10-C10</f>
         <v>-1152100</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="G10" s="23" t="s">
+      <c r="G10" s="21" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="C11" s="24" t="n">
+      <c r="C11" s="22" t="n">
         <v>62089068</v>
       </c>
-      <c r="D11" s="24" t="n">
+      <c r="D11" s="22" t="n">
         <v>62089068</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="22" t="n">
         <f aca="false">D11-C11</f>
         <v>0</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="G11" s="23" t="s">
+      <c r="G11" s="21" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="C12" s="24" t="n">
+      <c r="C12" s="22" t="n">
         <v>46124228</v>
       </c>
-      <c r="D12" s="24" t="n">
+      <c r="D12" s="22" t="n">
         <v>2198888</v>
       </c>
-      <c r="E12" s="24" t="n">
+      <c r="E12" s="22" t="n">
         <f aca="false">D12-C12</f>
         <v>-43925340</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="G12" s="23" t="s">
+      <c r="G12" s="21" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="22" t="n">
         <v>1511084</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="22" t="n">
         <v>25936424</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="22" t="n">
         <f aca="false">D13-C13</f>
         <v>24425340</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="G13" s="23" t="s">
+      <c r="G13" s="21" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="22" t="n">
         <v>10568020</v>
       </c>
-      <c r="D14" s="24" t="n">
+      <c r="D14" s="22" t="n">
         <v>7562450</v>
       </c>
-      <c r="E14" s="24" t="n">
+      <c r="E14" s="22" t="n">
         <f aca="false">D14-C14</f>
         <v>-3005570</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="G14" s="23" t="s">
+      <c r="G14" s="21" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="C15" s="24" t="n">
+      <c r="C15" s="22" t="n">
         <v>2628760</v>
       </c>
-      <c r="D15" s="24" t="n">
+      <c r="D15" s="22" t="n">
         <v>2628760</v>
       </c>
-      <c r="E15" s="24" t="n">
+      <c r="E15" s="22" t="n">
         <f aca="false">D15-C15</f>
         <v>0</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="G15" s="23" t="s">
+      <c r="G15" s="21" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="C16" s="24" t="n">
+      <c r="C16" s="22" t="n">
         <v>25850000</v>
       </c>
-      <c r="D16" s="24" t="n">
+      <c r="D16" s="22" t="n">
         <v>18127320</v>
       </c>
-      <c r="E16" s="24" t="n">
+      <c r="E16" s="22" t="n">
         <f aca="false">D16-C16</f>
         <v>-7722680</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="G16" s="23" t="s">
+      <c r="G16" s="21" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="C17" s="24" t="n">
+      <c r="C17" s="22" t="n">
         <v>13700000</v>
       </c>
-      <c r="D17" s="24" t="n">
+      <c r="D17" s="22" t="n">
         <v>13391680</v>
       </c>
-      <c r="E17" s="24" t="n">
+      <c r="E17" s="22" t="n">
         <f aca="false">D17-C17</f>
         <v>-308320</v>
       </c>
-      <c r="F17" s="22" t="s">
+      <c r="F17" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="23" t="s">
+      <c r="G17" s="21" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="C18" s="24" t="n">
+      <c r="C18" s="22" t="n">
         <v>22391000</v>
       </c>
-      <c r="D18" s="24" t="n">
+      <c r="D18" s="22" t="n">
         <v>22391000</v>
       </c>
-      <c r="E18" s="24" t="n">
+      <c r="E18" s="22" t="n">
         <f aca="false">D18-C18</f>
         <v>0</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="G18" s="23" t="s">
+      <c r="G18" s="21" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="C19" s="24" t="n">
+      <c r="C19" s="22" t="n">
         <v>14450000</v>
       </c>
-      <c r="D19" s="24" t="n">
+      <c r="D19" s="22" t="n">
         <v>14450000</v>
       </c>
-      <c r="E19" s="24" t="n">
+      <c r="E19" s="22" t="n">
         <f aca="false">D19-C19</f>
         <v>0</v>
       </c>
-      <c r="F19" s="22" t="s">
+      <c r="F19" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="G19" s="23" t="s">
+      <c r="G19" s="21" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="C20" s="24" t="n">
+      <c r="C20" s="22" t="n">
         <v>1631000</v>
       </c>
-      <c r="D20" s="24" t="n">
+      <c r="D20" s="22" t="n">
         <v>1631000</v>
       </c>
-      <c r="E20" s="24" t="n">
+      <c r="E20" s="22" t="n">
         <f aca="false">D20-C20</f>
         <v>0</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="G20" s="23" t="s">
+      <c r="G20" s="21" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="C21" s="24" t="n">
+      <c r="C21" s="22" t="n">
         <v>39800000</v>
       </c>
-      <c r="D21" s="24" t="n">
+      <c r="D21" s="22" t="n">
         <v>31230000</v>
       </c>
-      <c r="E21" s="24" t="n">
+      <c r="E21" s="22" t="n">
         <f aca="false">D21-C21</f>
         <v>-8570000</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="F21" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="G21" s="23" t="s">
+      <c r="G21" s="21" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6"/>
+      <c r="B22" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="C22" s="27" t="n">
+      <c r="C22" s="23" t="n">
         <f aca="false">SUM(C5:C21)</f>
         <v>305000000</v>
       </c>
-      <c r="D22" s="27" t="n">
+      <c r="D22" s="23" t="n">
         <f aca="false">SUM(D5:D21)</f>
         <v>262000000</v>
       </c>
-      <c r="E22" s="27" t="n">
+      <c r="E22" s="23" t="n">
         <f aca="false">D22-C22</f>
         <v>-43000000</v>
       </c>
-      <c r="F22" s="26"/>
-      <c r="G22" s="25" t="s">
+      <c r="F22" s="7"/>
+      <c r="G22" s="6" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="26"/>
-      <c r="B23" s="26" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="C23" s="27" t="n">
+      <c r="C23" s="23" t="n">
         <v>30500000</v>
       </c>
-      <c r="D23" s="27" t="n">
+      <c r="D23" s="23" t="n">
         <v>26200000</v>
       </c>
-      <c r="E23" s="27" t="n">
+      <c r="E23" s="23" t="n">
         <f aca="false">D23-C23</f>
         <v>-4300000</v>
       </c>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="26"/>
-      <c r="B24" s="26" t="s">
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C24" s="27" t="n">
+      <c r="C24" s="23" t="n">
         <f aca="false">C22+C23</f>
         <v>335500000</v>
       </c>
-      <c r="D24" s="27" t="n">
+      <c r="D24" s="23" t="n">
         <f aca="false">D22+D23</f>
         <v>288200000</v>
       </c>
-      <c r="E24" s="27" t="n">
+      <c r="E24" s="23" t="n">
         <f aca="false">D24-C24</f>
         <v>-47300000</v>
       </c>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="19" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C27" s="28" t="n">
+      <c r="C27" s="24" t="n">
         <v>335500000</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="19" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C28" s="28" t="n">
+      <c r="C28" s="24" t="n">
         <v>67100000</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="19" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C29" s="28" t="n">
+      <c r="C29" s="24" t="n">
         <v>215600000</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="19" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C30" s="28" t="n">
+      <c r="C30" s="24" t="n">
         <v>74800000</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="19" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C31" s="28" t="n">
+      <c r="C31" s="24" t="n">
         <v>693000000</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="19" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C32" s="28" t="n">
+      <c r="C32" s="24" t="n">
         <v>630000000</v>
       </c>
     </row>
@@ -4606,138 +3860,138 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="21" t="s">
         <v>215</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="25" t="s">
         <v>217</v>
       </c>
-      <c r="E2" s="31" t="n">
+      <c r="E2" s="26" t="n">
         <v>301000</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="21" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="21" t="s">
         <v>220</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="21" t="s">
         <v>221</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="E3" s="31" t="n">
+      <c r="E3" s="26" t="n">
         <v>374000</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="F3" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="G3" s="30"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="21" t="s">
         <v>220</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="31" t="n">
+      <c r="E4" s="26" t="n">
         <v>100000</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="G4" s="21" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="25" t="s">
         <v>226</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="25" t="s">
         <v>217</v>
       </c>
-      <c r="E5" s="31" t="n">
+      <c r="E5" s="26" t="n">
         <v>50120</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="27" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="21" t="s">
         <v>230</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="21" t="s">
         <v>231</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D6" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="31" t="n">
+      <c r="E6" s="26" t="n">
         <v>369000</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="21" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="21" t="s">
         <v>220</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="21" t="s">
         <v>233</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="E7" s="31" t="n">
+      <c r="E7" s="26" t="n">
         <v>61600</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="F7" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="G7" s="21" t="s">
         <v>234</v>
       </c>
     </row>
@@ -4760,369 +4014,369 @@
   <dimension ref="A1:C43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="32" t="s">
+    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="19" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="33" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="29" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="29" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="C5" s="29"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="29" t="n">
+      <c r="C5" s="25"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="21" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="29" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="C7" s="29"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="29" t="n">
+      <c r="C7" s="25"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="C8" s="29"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="29" t="n">
+      <c r="C8" s="25"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="21" t="s">
         <v>244</v>
       </c>
-      <c r="C9" s="29"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="29" t="n">
+      <c r="C9" s="25"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="21" t="s">
         <v>245</v>
       </c>
-      <c r="C10" s="29"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="29" t="n">
+      <c r="C10" s="25"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="21" t="s">
         <v>246</v>
       </c>
-      <c r="C11" s="29"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="29" t="n">
+      <c r="C11" s="25"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="C12" s="29"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="29" t="n">
+      <c r="C12" s="25"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="21" t="s">
         <v>248</v>
       </c>
-      <c r="C13" s="29"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="29" t="n">
+      <c r="C13" s="25"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="21" t="s">
         <v>249</v>
       </c>
-      <c r="C14" s="29"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="29" t="n">
+      <c r="C14" s="25"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="21" t="s">
         <v>250</v>
       </c>
-      <c r="C15" s="29"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="29" t="n">
+      <c r="C15" s="25"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="C16" s="29"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="29" t="n">
+      <c r="C16" s="25"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="C17" s="29"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="29" t="n">
+      <c r="C17" s="25"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="29" t="n">
+      <c r="C18" s="25"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="25" t="s">
         <v>254</v>
       </c>
-      <c r="C19" s="29"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="29" t="n">
+      <c r="C19" s="25"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="25" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="C20" s="29"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="29" t="n">
+      <c r="C20" s="25"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="25" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="C21" s="29"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="29" t="n">
+      <c r="C21" s="25"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="25" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="C22" s="29"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="29" t="n">
+      <c r="C22" s="25"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="25" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="C23" s="29"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="29" t="n">
+      <c r="C23" s="25"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="C24" s="29"/>
-    </row>
-    <row r="25" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="29" t="n">
+      <c r="C24" s="25"/>
+    </row>
+    <row r="25" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="25" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="21" t="s">
         <v>260</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="25" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="29" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="25" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="21" t="s">
         <v>262</v>
       </c>
-      <c r="C26" s="29"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="29" t="n">
+      <c r="C26" s="25"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="25" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="25" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="29" t="n">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="C28" s="29"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="29" t="n">
+      <c r="C28" s="25"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="21" t="s">
         <v>266</v>
       </c>
-      <c r="C29" s="29"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="29" t="n">
+      <c r="C29" s="25"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="C30" s="29"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="29" t="n">
+      <c r="C30" s="25"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="25" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="23" t="s">
+      <c r="B31" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="C31" s="29"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="29" t="n">
+      <c r="C31" s="25"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="25" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="23" t="s">
+      <c r="B32" s="21" t="s">
         <v>269</v>
       </c>
-      <c r="C32" s="29"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="29" t="n">
+      <c r="C32" s="25"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="25" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="23" t="s">
+      <c r="B33" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="C33" s="29"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="29" t="n">
+      <c r="C33" s="25"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="29" t="s">
+      <c r="B34" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="C34" s="29"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="29" t="n">
+      <c r="C34" s="25"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="23" t="s">
+      <c r="B35" s="21" t="s">
         <v>272</v>
       </c>
-      <c r="C35" s="29"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="29" t="n">
+      <c r="C35" s="25"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="25" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="23" t="s">
+      <c r="B36" s="21" t="s">
         <v>273</v>
       </c>
-      <c r="C36" s="29"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="29" t="n">
+      <c r="C36" s="25"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="25" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="23" t="s">
+      <c r="B37" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="C37" s="29"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="29" t="n">
+      <c r="C37" s="25"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="23" t="s">
+      <c r="B38" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="C38" s="29"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="29" t="n">
+      <c r="C38" s="25"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="25" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="23" t="s">
+      <c r="B39" s="21" t="s">
         <v>276</v>
       </c>
-      <c r="C39" s="29"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="29" t="n">
+      <c r="C39" s="25"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="23" t="s">
+      <c r="B40" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="C40" s="29"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C40" s="25"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="19" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="3" t="s">
         <v>279</v>
       </c>
     </row>

--- a/椙山改修/増減_見積内訳_索引.xlsx
+++ b/椙山改修/増減_見積内訳_索引.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">出典：椙山改修/参考/260904_見積内訳書（契約・原価）.pdf（2026/9/4 出力、101頁。左＝見積、右＝原価）</t>
   </si>
   <si>
-    <t xml:space="preserve">基準金額（契約金額）：契約書待ち。5/28 見積（No.260007）と 9/4 見積内訳書のどちらが契約の基準かは契約書で確定する</t>
+    <t xml:space="preserve">基準金額（契約金額）：262,000,000（税抜）／288,200,000（税込）、9/4 見積内訳書による（10/31 小山さん確認）。食堂分だけを基準とする（外構3エリアが同じ契約かは未確認）</t>
   </si>
   <si>
     <t xml:space="preserve">階層</t>
@@ -563,7 +563,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">基準金額：契約書待ち。理由欄は【事実】＝両方の明細で確認、【推測】＝明細の照合はしていない／理由は書類に書かれていない</t>
+    <t xml:space="preserve">基準金額：9/4 見積内訳書の 262,000,000（税抜）＝契約金額（10/31 小山さん確認）。理由欄は【事実】＝両方の明細で確認、【推測】＝明細の照合はしていない／理由は書類に書かれていない</t>
   </si>
   <si>
     <t xml:space="preserve">工種</t>
@@ -1071,72 +1071,7 @@
     <t xml:space="preserve">含まれる</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">吹き抜け側は契約内。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">階プランターの内側（室内側）の撤去は契約外 → 追加見積 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">650,000 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を提出、不採用（撤去しない）（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10/31 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">小山さん確認）</t>
-    </r>
+    <t xml:space="preserve">吹き抜け側は契約内。2階プランターの内側（室内側）の撤去は契約外 → 追加見積 650,000 を提出、不採用（撤去しない）（10/31 小山さん確認）</t>
   </si>
   <si>
     <t xml:space="preserve">既存設備（オペレーター）の対応</t>
@@ -1560,7 +1495,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1666,10 +1601,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3945,7 +3876,7 @@
       <c r="F5" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="21" t="s">
         <v>229</v>
       </c>
     </row>
@@ -4030,13 +3961,13 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="28" t="s">
         <v>238</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>214</v>
       </c>
     </row>

--- a/椙山改修/増減_見積内訳_索引.xlsx
+++ b/椙山改修/増減_見積内訳_索引.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">出典：椙山改修/参考/260904_見積内訳書（契約・原価）.pdf（2026/9/4 出力、101頁。左＝見積、右＝原価）</t>
   </si>
   <si>
-    <t xml:space="preserve">基準金額（契約金額）：262,000,000（税抜）／288,200,000（税込）、9/4 見積内訳書による（10/31 小山さん確認）。食堂分だけを基準とする（外構3エリアが同じ契約かは未確認）</t>
+    <t xml:space="preserve">基準金額（契約金額）：契約は1本（食堂＋外構3エリア、10/31 小山さん確認）。食堂分 262,000,000（税抜）／288,200,000（税込）＝9/4 見積内訳書（確定）。外構3エリア分は確認中（参考：5/28 見積 No.260007 税込 さくら坂 67,100,000／キャンパスコモン 215,600,000／10000歩コース 74,800,000）</t>
   </si>
   <si>
     <t xml:space="preserve">階層</t>
@@ -563,7 +563,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">基準金額：9/4 見積内訳書の 262,000,000（税抜）＝契約金額（10/31 小山さん確認）。理由欄は【事実】＝両方の明細で確認、【推測】＝明細の照合はしていない／理由は書類に書かれていない</t>
+    <t xml:space="preserve">契約は1本（食堂＋外構3エリア）。食堂分の契約金額＝9/4 見積内訳書 262,000,000（税抜、10/31 小山さん確認）。外構3エリア分は確認中。理由欄は【事実】＝両方の明細で確認、【推測】＝明細の照合はしていない／理由は書類に書かれていない</t>
   </si>
   <si>
     <t xml:space="preserve">工種</t>

--- a/椙山改修/増減_見積内訳_索引.xlsx
+++ b/椙山改修/増減_見積内訳_索引.xlsx
@@ -1221,7 +1221,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">には金属製建具工事に「スライディンウォール」</t>
+      <t xml:space="preserve">の「スライディンウォール」</t>
     </r>
     <r>
       <rPr>
@@ -1231,7 +1231,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2,239,000 </t>
+      <t xml:space="preserve">2,239,000</t>
     </r>
     <r>
       <rPr>
@@ -1240,7 +1240,121 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">が計上されている（別途工事の記載との関係は要確認）</t>
+      <t xml:space="preserve">（製品代 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,599,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋取付運搬費 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">640,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）と同じもの（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/31 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小山さん確認）。契約（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）では本工事に含まれる。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5/28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の別途工事欄の記載は定型文か </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5/28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時点の扱いと思われる（推測）</t>
     </r>
   </si>
   <si>

--- a/椙山改修/増減_見積内訳_索引.xlsx
+++ b/椙山改修/増減_見積内訳_索引.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">出典：椙山改修/参考/260904_見積内訳書（契約・原価）.pdf（2026/9/4 出力、101頁。左＝見積、右＝原価）</t>
   </si>
   <si>
-    <t xml:space="preserve">基準金額（契約金額）：契約は1本（食堂＋外構3エリア、10/31 小山さん確認）。食堂分 262,000,000（税抜）／288,200,000（税込）＝9/4 見積内訳書（確定）。外構3エリア分は確認中（参考：5/28 見積 No.260007 税込 さくら坂 67,100,000／キャンパスコモン 215,600,000／10000歩コース 74,800,000）</t>
+    <t xml:space="preserve">基準金額（契約金額）：契約は1本（食堂＋外構3エリア、10/31 小山さん確認）。食堂分 262,000,000（税抜）／288,200,000（税込）＝9/4 見積内訳書（確定）。外構3エリア分の契約金額は扱わない（10/31 小山さん指示）。増減リストは食堂分 262,000,000 を基準とする（参考：5/28 見積 No.260007 税込 さくら坂 67,100,000／キャンパスコモン 215,600,000／10000歩コース 74,800,000）</t>
   </si>
   <si>
     <t xml:space="preserve">階層</t>
@@ -563,7 +563,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">契約は1本（食堂＋外構3エリア）。食堂分の契約金額＝9/4 見積内訳書 262,000,000（税抜、10/31 小山さん確認）。外構3エリア分は確認中。理由欄は【事実】＝両方の明細で確認、【推測】＝明細の照合はしていない／理由は書類に書かれていない</t>
+    <t xml:space="preserve">契約は1本（食堂＋外構3エリア）。食堂分の契約金額＝9/4 見積内訳書 262,000,000（税抜、10/31 小山さん確認）。外構3エリア分の契約金額は扱わない（10/31 小山さん指示）。理由欄は【事実】＝両方の明細で確認、【推測】＝明細の照合はしていない／理由は書類に書かれていない</t>
   </si>
   <si>
     <t xml:space="preserve">工種</t>
